--- a/artfynd/A 39320-2024 artfynd.xlsx
+++ b/artfynd/A 39320-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,6 +1160,120 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123758117</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56796</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gömminge, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>594352</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6287865</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Glömminge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39320-2024 artfynd.xlsx
+++ b/artfynd/A 39320-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>123758117</v>
       </c>
       <c r="B6" t="n">
-        <v>56796</v>
+        <v>56799</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39320-2024 artfynd.xlsx
+++ b/artfynd/A 39320-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87381</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
           <t>Svampinventeringar i Mittlandet 2018-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88642281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/387850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
           <t>Inventering av Ölands kärlväxtflora., Hässleinventering för Lst 2018-2019</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81781849</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/625987</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123758117</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2222264</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3932309</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3933960</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4240264</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,8 +1934,26 @@
           <t>Inventering av Ölands kärlväxtflora., Hässleinventering för Lst 2018-2019</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81781850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>